--- a/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -329,16 +329,16 @@
 </t>
   </si>
   <si>
-    <t>リソースに関するメタデータ / Metadata about the resource</t>
-  </si>
-  <si>
-    <t>リソースに関するメタデータ。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -464,7 +464,7 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -575,13 +575,13 @@
     <t>アプリケーションは、identifierが一時的であると明示的に述べられない限り、永続的であると想定できる。</t>
   </si>
   <si>
-    <t>特定の使用のコンテキストが一連の識別子の中から選択される適切な識別子を許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>既知の場合、この識別子の目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
+    <t>既知の場合、このidentifierの目的を識別します。 / Identifies the purpose for this identifier, if known .</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
@@ -600,22 +600,22 @@
 </t>
   </si>
   <si>
-    <t>識別子の説明 / Description of identifier</t>
-  </si>
-  <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>この要素は、識別子の一般的なカテゴリのみを扱います。識別子。システムに対応するコードに使用しないでください。一部の識別子は、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明な識別子を処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>識別子システムが不明な場合、ユーザーは識別子を使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>特定の目的に使用する識別子を決定するために使用できる識別子のコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
@@ -630,16 +630,16 @@
     <t>Observation.identifier.system</t>
   </si>
   <si>
-    <t>識別子値の名前空間 / The namespace for the identifier value</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
   </si>
   <si>
     <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>識別子。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>識別子のセットがたくさんあります。2つの識別子を一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意の識別子セットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>Identifier.system</t>
@@ -660,7 +660,7 @@
     <t>システムのコンテキスト内で一意の識別子となる文字列を設定。</t>
   </si>
   <si>
-    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。識別子。価値は、識別子の知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>Identifier.value</t>
@@ -682,7 +682,7 @@
     <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
   </si>
   <si>
-    <t>識別子が使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -704,10 +704,10 @@
     <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
   </si>
   <si>
-    <t>識別子を発行/管理する組織。 / Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>識別子は、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -829,10 +829,13 @@
     <t>どの観測値が取得されて表示されるかをフィルタリングするために使用されます。 / Used for filtering what observations are retrieved and displayed.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:$this}
+    <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:coding.system}
 </t>
   </si>
   <si>
@@ -897,112 +900,118 @@
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
-    <t>Observation.category:laboratory</t>
+    <t>Observation.category:first</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表から"laboratory"を設定する。</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「furst」固定とする。  
+(social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_SimpleObservationCategory_VS</t>
+  </si>
+  <si>
+    <t>Observation.category:first.id</t>
+  </si>
+  <si>
+    <t>Observation.category:first.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「laboratory」固定とする。</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.system</t>
+  </si>
+  <si>
+    <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表を使用する。</t>
+  </si>
+  <si>
+    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.version</t>
+  </si>
+  <si>
+    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.category:first.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.category.coding.code</t>
+  </si>
+  <si>
+    <t>検体検査を表すコード laboratory を設定する。</t>
+  </si>
+  <si>
+    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
   </si>
   <si>
     <t>laboratory</t>
   </si>
   <si>
-    <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表から"laboratory"を設定する。</t>
-  </si>
-  <si>
-    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「laboratory」固定とする。  
-(social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.id</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「laboratory」固定とする。</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.system</t>
-  </si>
-  <si>
-    <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表を使用する。</t>
-  </si>
-  <si>
-    <t>uriは、oid（urn：oid：...）またはuuid（urn：uuid：...）である場合があります。OIDとUUIDは、HL7 OIDレジストリへの参照となります。それ以外の場合、URIは、FHIRの特別なURIを定義したHL7のリストから来るか、システムを明確かつ明確に確立する定義を参照する必要があります。 / The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>シンボルの定義のソースについて明確である必要があります。 / Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.version</t>
-  </si>
-  <si>
-    <t>システムのバージョン - 関連する場合 / Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>このコードを選択するときに使用されたコードシステムのバージョン。コードの意味がバージョン全体で一貫しているため、適切にメンテナンスしたコードシステムでは報告されたバージョンを必要としないことに注意してください。ただし、これは一貫して保証することはできず、意味が一貫していることが保証されていない場合、バージョンを交換する必要があります。 / The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>用語がコードシステムバージョンを識別するために使用する文字列を明確に定義していない場合、推奨は、そのバージョンがバージョンの日付として公式に公開された日付（FHIR日付形式で表現）を使用することです。 / Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Observation.category:laboratory.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.category.coding.code</t>
-  </si>
-  <si>
-    <t>検体検査を表すコード laboratory を設定する。</t>
-  </si>
-  <si>
-    <t>システム内の特定のコードを参照する必要があります。 / Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
     <t>Coding.code</t>
   </si>
   <si>
@@ -1012,7 +1021,7 @@
     <t>./code</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.display</t>
+    <t>Observation.category:first.coding.display</t>
   </si>
   <si>
     <t>Observation.category.coding.display</t>
@@ -1036,7 +1045,7 @@
     <t>CV.displayName</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.coding.userSelected</t>
+    <t>Observation.category:first.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.category.coding.userSelected</t>
@@ -1067,7 +1076,7 @@
     <t>CD.codingRationale</t>
   </si>
   <si>
-    <t>Observation.category:laboratory.text</t>
+    <t>Observation.category:first.text</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1644,10 +1653,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1694,7 +1700,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Specimen_Common)
 </t>
   </si>
   <si>
@@ -1766,7 +1772,7 @@
     <t>どの値が「正常」と見なされるかを知ることは、特定の結果の意義を評価するのに役立つ。さまざまなコンテキストに対応するため複数の参照範囲を提供できる必要がある。</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
@@ -2386,7 +2392,7 @@
   <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.2265625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2410,7 +2416,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="145.265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -5152,15 +5158,17 @@
       <c r="X23" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="Y23" s="2"/>
+      <c r="Y23" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5194,10 +5202,10 @@
         <v>83</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>83</v>
@@ -5205,10 +5213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5323,10 +5331,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5443,10 +5451,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5469,19 +5477,19 @@
         <v>95</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5530,7 +5538,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5551,10 +5559,10 @@
         <v>83</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
@@ -5565,10 +5573,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5594,16 +5602,16 @@
         <v>162</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5652,7 +5660,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5673,10 +5681,10 @@
         <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
@@ -5687,13 +5695,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>255</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>83</v>
@@ -5703,7 +5711,7 @@
         <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>
@@ -5718,13 +5726,13 @@
         <v>184</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O28" t="s" s="2">
         <v>258</v>
@@ -5756,7 +5764,7 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5798,10 +5806,10 @@
         <v>83</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>83</v>
@@ -5809,10 +5817,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5927,10 +5935,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6047,10 +6055,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6058,10 +6066,10 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -6073,19 +6081,19 @@
         <v>95</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>83</v>
@@ -6134,7 +6142,7 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6155,10 +6163,10 @@
         <v>83</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
@@ -6169,10 +6177,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6287,10 +6295,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6407,10 +6415,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6436,23 +6444,23 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>83</v>
@@ -6494,7 +6502,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6515,10 +6523,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6529,10 +6537,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6558,13 +6566,13 @@
         <v>162</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6614,7 +6622,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6635,10 +6643,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6649,10 +6657,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6678,21 +6686,21 @@
         <v>114</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>83</v>
@@ -6734,7 +6742,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6755,10 +6763,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6769,10 +6777,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6798,14 +6806,14 @@
         <v>162</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6854,7 +6862,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6875,10 +6883,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6889,10 +6897,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6915,19 +6923,19 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6976,7 +6984,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6997,10 +7005,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -7011,10 +7019,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7040,16 +7048,16 @@
         <v>162</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7098,7 +7106,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7119,10 +7127,10 @@
         <v>83</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -7133,14 +7141,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7162,16 +7170,16 @@
         <v>184</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
@@ -7199,10 +7207,10 @@
         <v>118</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>83</v>
@@ -7220,7 +7228,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>94</v>
@@ -7235,30 +7243,30 @@
         <v>106</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7373,10 +7381,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7493,10 +7501,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7519,19 +7527,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7580,7 +7588,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7601,10 +7609,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7615,10 +7623,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7733,10 +7741,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7853,10 +7861,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7882,16 +7890,16 @@
         <v>108</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
@@ -7940,7 +7948,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7961,10 +7969,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7975,10 +7983,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8004,13 +8012,13 @@
         <v>162</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8060,7 +8068,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8081,10 +8089,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8095,10 +8103,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8124,16 +8132,16 @@
         <v>114</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -8182,7 +8190,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8203,10 +8211,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8217,10 +8225,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8246,16 +8254,16 @@
         <v>162</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8304,7 +8312,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8325,10 +8333,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8339,10 +8347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8365,19 +8373,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8426,7 +8434,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8447,10 +8455,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8461,10 +8469,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8490,16 +8498,16 @@
         <v>162</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8548,7 +8556,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8569,10 +8577,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8583,10 +8591,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8609,19 +8617,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8670,7 +8678,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8685,19 +8693,19 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8705,10 +8713,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8731,16 +8739,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8790,7 +8798,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8811,13 +8819,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8825,14 +8833,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8851,19 +8859,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8912,7 +8920,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8927,19 +8935,19 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
@@ -8947,14 +8955,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8973,19 +8981,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9034,7 +9042,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9049,19 +9057,19 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9069,10 +9077,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9095,16 +9103,16 @@
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9154,7 +9162,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9175,13 +9183,13 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9189,10 +9197,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9215,19 +9223,19 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9276,7 +9284,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9291,19 +9299,19 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9311,10 +9319,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9337,19 +9345,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9386,17 +9394,17 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9405,7 +9413,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9414,30 +9422,30 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>83</v>
@@ -9459,19 +9467,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9520,7 +9528,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9529,7 +9537,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9538,30 +9546,30 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>83</v>
@@ -9586,16 +9594,16 @@
         <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9644,7 +9652,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9653,7 +9661,7 @@
         <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>106</v>
@@ -9662,30 +9670,30 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>83</v>
@@ -9710,16 +9718,16 @@
         <v>162</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9768,7 +9776,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9777,7 +9785,7 @@
         <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>106</v>
@@ -9786,27 +9794,27 @@
         <v>83</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9832,16 +9840,16 @@
         <v>184</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9869,10 +9877,10 @@
         <v>189</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>83</v>
@@ -9890,7 +9898,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9899,7 +9907,7 @@
         <v>94</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -9914,7 +9922,7 @@
         <v>137</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9925,14 +9933,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9954,16 +9962,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9991,10 +9999,10 @@
         <v>189</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -10012,7 +10020,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10030,27 +10038,27 @@
         <v>83</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10073,19 +10081,19 @@
         <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10134,7 +10142,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10155,10 +10163,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10169,10 +10177,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10287,10 +10295,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10407,10 +10415,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10433,16 +10441,16 @@
         <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10492,7 +10500,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10516,7 +10524,7 @@
         <v>137</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10527,10 +10535,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10553,13 +10561,13 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10610,7 +10618,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10634,7 +10642,7 @@
         <v>137</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
@@ -10645,10 +10653,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10671,16 +10679,16 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10730,7 +10738,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>94</v>
@@ -10754,7 +10762,7 @@
         <v>137</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10765,10 +10773,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10794,13 +10802,13 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10826,31 +10834,29 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="Y70" s="2"/>
+      <c r="Z70" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="Y70" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10868,27 +10874,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10914,16 +10920,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10948,13 +10954,13 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10972,7 +10978,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10993,10 +10999,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11007,10 +11013,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11033,16 +11039,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11092,7 +11098,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11110,27 +11116,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11153,16 +11159,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11212,7 +11218,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11230,27 +11236,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11273,19 +11279,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11334,7 +11340,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11346,7 +11352,7 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
@@ -11355,10 +11361,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11369,10 +11375,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11487,10 +11493,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11607,14 +11613,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11636,10 +11642,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -11694,7 +11700,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11729,10 +11735,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11755,16 +11761,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11814,7 +11820,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11823,7 +11829,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11835,10 +11841,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11849,10 +11855,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11875,16 +11881,16 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11934,7 +11940,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11943,7 +11949,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11955,10 +11961,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11969,10 +11975,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11998,16 +12004,16 @@
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12035,10 +12041,10 @@
         <v>118</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12056,7 +12062,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12074,13 +12080,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12091,10 +12097,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12120,16 +12126,16 @@
         <v>184</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12154,13 +12160,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12178,7 +12184,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12196,13 +12202,13 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12213,10 +12219,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12239,19 +12245,19 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12300,7 +12306,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12324,7 +12330,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12335,10 +12341,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12364,13 +12370,13 @@
         <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12420,7 +12426,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12441,10 +12447,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12455,10 +12461,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12481,16 +12487,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12540,7 +12546,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12561,10 +12567,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12575,10 +12581,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12601,16 +12607,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12660,7 +12666,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12681,10 +12687,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12695,10 +12701,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12721,19 +12727,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12782,7 +12788,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12803,10 +12809,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12817,10 +12823,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12935,10 +12941,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13055,14 +13061,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13084,10 +13090,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>143</v>
@@ -13142,7 +13148,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13177,10 +13183,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13206,16 +13212,16 @@
         <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13240,13 +13246,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13264,7 +13270,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13282,16 +13288,16 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
@@ -13299,10 +13305,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13325,19 +13331,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13386,7 +13392,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13404,27 +13410,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13450,16 +13456,16 @@
         <v>184</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13487,10 +13493,10 @@
         <v>189</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13508,7 +13514,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13517,7 +13523,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13532,7 +13538,7 @@
         <v>137</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13543,14 +13549,14 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13572,16 +13578,16 @@
         <v>184</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13609,10 +13615,10 @@
         <v>189</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13630,7 +13636,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13648,27 +13654,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13694,16 +13700,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13752,7 +13758,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13773,10 +13779,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3648" uniqueCount="653">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3649" uniqueCount="654">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a</t>
+    <t>1.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -282,7 +282,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}obs-6:databsentrasonは、観察.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:visserveration.codeがvisserveration.component.codeと同じ場合、コードに関連付けられている値要素が存在しないでください / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReasonは、Observation.value [x]が存在しない場合にのみ存在するものとします / dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:Observation.codeがObservation.component.codeと同じ場合、そのcodeに関連付くvalueは存在してはならない。 / If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}</t>
   </si>
   <si>
     <t>Event</t>
@@ -909,7 +909,7 @@
     <t>検体検査では、http://jpfhir.jp/fhir/core/CodeSystem/JP_SimpleObservationCategory_CS のコード表から"laboratory"を設定する。</t>
   </si>
   <si>
-    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「furst」固定とする。  
+    <t>【JP Core仕様】推奨コード表「JP Core Simple Observation Category CodeSystem」より、このプロファイルでは「laboratory」固定とする。  
 (social-history | vital-signs | imaging | laboratory | procedure | survey | exam | therapy | activity)</t>
   </si>
   <si>
@@ -1292,7 +1292,7 @@
 PeriodTiming</t>
   </si>
   <si>
-    <t>取得された結果が臨床的に確定された日時または期間</t>
+    <t>検体を採取した日時または期間</t>
   </si>
   <si>
     <t>検体検査の場合は、検体採取日時。</t>
@@ -1381,7 +1381,7 @@
 CodeableConceptstring</t>
   </si>
   <si>
-    <t>同じ検査項目でも、システム（施設）により、使うデータ型が異なる可能性あり【詳細参照】</t>
+    <t>検体検査結果の値</t>
   </si>
   <si>
     <t>検体検査の結果として決定された情報。</t>
@@ -1494,7 +1494,7 @@
     <t>多くの結果には、測定で例外的な値を処理する必要があります。 / For many results it is necessary to handle exceptional values in measurements.</t>
   </si>
   <si>
-    <t>結果（ `balue.value [x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+    <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
@@ -1653,7 +1653,10 @@
     <t>example</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_Observation_BodySite_VS</t>
+    <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1773,7 +1776,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:少なくとも低いまたは高またはテキストが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+obs-3:少なくともlow, high, textのいずれかが必要です / Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
   </si>
   <si>
     <t>OBX.7</t>
@@ -1847,7 +1850,7 @@
     <t>Observation.referenceRange.type</t>
   </si>
   <si>
-    <t>参照範囲予選 / Reference range qualifier</t>
+    <t>参照範囲予選修飾子 / Reference range qualifier</t>
   </si>
   <si>
     <t>対象となる母集団のどの部分に適用するかを示すコード。正常範囲、要治療範囲、など。</t>
@@ -2054,7 +2057,7 @@
   </si>
   <si>
     <t>「null」または例外的な値は、FHIR観測で2つの方法を表すことができます。1つの方法は、それらを単に値セットに含めるだけで、値の例外を表すことです。たとえば、血清学テストの測定値は、「検出」、「検出されない」、「決定的でない」、または「テストなし」です。
-別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、DataBsentrasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
+別の方法は、実際の観測に値要素を使用し、明示的なDataBsEntreason要素を使用して例外的な値を記録することです。たとえば、測定が完了していないときに、dataAbsentReasonコード「エラー」を使用できます。これらのオプションのため、一般的な観測を例外的な価値のために解釈するには、ユースケース契約が必要です。 / "Null" or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "test not done". 
 The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed.  Because of these options, use-case agreements are required to interpret general observations for exceptional values.</t>
   </si>
   <si>
@@ -5711,7 +5714,7 @@
         <v>94</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>83</v>
@@ -10836,9 +10839,11 @@
       <c r="X70" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Y70" s="2"/>
+      <c r="Y70" t="s" s="2">
+        <v>516</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10874,27 +10879,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10920,16 +10925,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10957,10 +10962,10 @@
         <v>515</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10978,7 +10983,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10999,10 +11004,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11013,10 +11018,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11039,16 +11044,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11098,7 +11103,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11116,27 +11121,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11159,16 +11164,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11218,7 +11223,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11236,27 +11241,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11279,19 +11284,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11340,7 +11345,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11352,7 +11357,7 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
@@ -11361,10 +11366,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11375,10 +11380,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11493,10 +11498,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11613,14 +11618,14 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11642,10 +11647,10 @@
         <v>140</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>143</v>
@@ -11700,7 +11705,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11735,10 +11740,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11761,16 +11766,16 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11820,7 +11825,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11829,7 +11834,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11841,10 +11846,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11855,10 +11860,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11881,16 +11886,16 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11940,7 +11945,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11949,7 +11954,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11961,10 +11966,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11975,10 +11980,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12004,16 +12009,16 @@
         <v>184</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12041,10 +12046,10 @@
         <v>118</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12062,7 +12067,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12080,10 +12085,10 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>480</v>
@@ -12097,10 +12102,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12126,16 +12131,16 @@
         <v>184</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12163,10 +12168,10 @@
         <v>515</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12184,7 +12189,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12202,10 +12207,10 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>480</v>
@@ -12219,10 +12224,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12245,19 +12250,19 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12306,7 +12311,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12330,7 +12335,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12341,10 +12346,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12370,10 +12375,10 @@
         <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N83" t="s" s="2">
         <v>371</v>
@@ -12426,7 +12431,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12447,10 +12452,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12461,10 +12466,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12487,16 +12492,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12546,7 +12551,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12567,10 +12572,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12581,10 +12586,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12607,16 +12612,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12666,7 +12671,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12687,10 +12692,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12701,10 +12706,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12727,19 +12732,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12788,7 +12793,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12809,10 +12814,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12823,10 +12828,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12941,10 +12946,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13061,14 +13066,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13090,10 +13095,10 @@
         <v>140</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>143</v>
@@ -13148,7 +13153,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13183,10 +13188,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13212,13 +13217,13 @@
         <v>184</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>346</v>
@@ -13249,10 +13254,10 @@
         <v>515</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13270,7 +13275,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13288,7 +13293,7 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>351</v>
@@ -13305,10 +13310,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13331,16 +13336,16 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>439</v>
@@ -13392,7 +13397,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13410,7 +13415,7 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>444</v>
@@ -13427,10 +13432,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13456,13 +13461,13 @@
         <v>184</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>465</v>
@@ -13514,7 +13519,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13549,10 +13554,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13578,16 +13583,16 @@
         <v>184</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13636,7 +13641,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13671,10 +13676,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13700,16 +13705,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13758,7 +13763,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13779,10 +13784,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
@@ -2395,15 +2395,15 @@
   <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="44.67578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2414,28 +2414,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="155.12109375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="63.09375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.09375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04</t>
+    <t>2025-07-30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
@@ -383,7 +383,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -618,7 +618,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -697,7 +697,7 @@
     <t>Observation.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -832,7 +832,7 @@
     <t>高レベルの観測カテゴリのコード。 / Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:coding.system}
@@ -1232,7 +1232,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1497,7 +1497,7 @@
     <t>結果（ `Observation.value[x]`）が欠落している理由を指定するコード。 / Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1531,7 +1531,7 @@
     <t>観測の解釈を識別するコード。 / Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1581,7 +1581,7 @@
     <t>Observation.note.author[x]</t>
   </si>
   <si>
-    <t>Reference(Practitioner|Patient|RelatedPerson|Organization)
+    <t>Reference(Practitioner|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 string</t>
   </si>
   <si>
@@ -1656,7 +1656,7 @@
     <t>解剖学的場所を説明するコード。左右性が含まれる場合があります。 / Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1691,7 +1691,7 @@
     <t>単純な観測の方法。 / Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1731,7 +1731,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1812,7 +1812,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1865,7 +1865,7 @@
     <t>参照範囲の意味のコード。 / Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1898,7 +1898,7 @@
     <t>参照範囲が適用される母集団を識別するコード。 / Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2021,7 +2021,7 @@
     <t>単純な観測の名前を識別するコード。 / Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR 
--- a/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/main/StructureDefinition-jp-observation-labresult.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
